--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultimate_광기" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DynamicDifficulty" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herald_충신" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,167 +620,224 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>상수</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>baseMaxHp</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>시작 최대 체력</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>화폐=송곳니. 사망 시 적립: (킬+생존초+레벨×8)×(1+0.12×gain Lv). 비용=기본가×1.55^Lv. localStorage 영구 저장.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>baseSpeed</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>기본 이동속도(px/s)</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>효과(레벨당)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>기본가</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>최대Lv</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>비용증가</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>pickupRange</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>58</v>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>💪</t>
+        </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>구슬 수집 기본 범위</t>
+          <t>맹수의 발톱</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>시작 공격력 +5%</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>xpStart</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>❤</t>
+        </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>레벨1 요구 XP</t>
+          <t>두꺼운 가죽</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>시작 체력 +15</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>xpGrowth</t>
+          <t>spd</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>prev×1.26+2</t>
+          <t>🌬</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>다음 레벨 요구 XP</t>
+          <t>바람의 다리</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>시작 이동속도 +4%</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>enemyCap</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>120</v>
+          <t>pick</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>🧲</t>
+        </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>동시 최대 적</t>
+          <t>굶주린 코</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>수집 범위 +8</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>bossInterval</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>90</v>
+          <t>gain</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>🦷</t>
+        </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>보스 주기(초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>rageMax</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>광기 게이지 최대</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>diffRange</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>0.6~2.2</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>동적 난이도 배수 범위</t>
+          <t>전리품 사냥꾼</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>송곳니 획득 +12%</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>×1.55</t>
         </is>
       </c>
     </row>
@@ -794,7 +852,182 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>상수</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>baseMaxHp</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>시작 최대 체력</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>baseSpeed</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>기본 이동속도(px/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>pickupRange</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>구슬 수집 기본 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>xpStart</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>레벨1 요구 XP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>xpGrowth</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>prev×1.26+2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>다음 레벨 요구 XP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>enemyCap</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>동시 최대 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>bossInterval</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>보스 주기(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>rageMax</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>광기 게이지 최대</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>diffRange</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>0.6~2.2</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>동적 난이도 배수 범위</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -912,24 +1145,24 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>포식(Devour): 삼켜 회복 + 시각적 성장</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>메타 영구강화(송곳니 화폐 → 전리품 상점) + 위협도 표시</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>다음</t>
+          <t>다음★</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>메타 영구성장 상점(골드 해금)</t>
+          <t>포식(Devour): 삼켜 회복 + 시각적 성장</t>
         </is>
       </c>
     </row>
@@ -939,9 +1172,21 @@
           <t>다음</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>보스 패턴·서사 / CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>
       </c>
     </row>
@@ -950,7 +1195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1157,24 +1157,24 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>포식(Devour): 삼켜 회복 + 시각적 성장</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>무해·귀여움 컨셉: 캐릭터 절차 애니메이션(숨쉬기·통통·눈깜빡·꼬리)+캐릭터별 외형, 타이니 등장연출</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>다음</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>귀여운 코스메틱 스킨(윤리적 수익화) / 포식(Devour)</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,19 @@
           <t>다음</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1169,24 +1169,24 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>다음★</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>귀여운 코스메틱 스킨(윤리적 수익화) / 포식(Devour)</t>
+          <t>타이니 호출 메뉴·고정 반투명 조이스틱·STAGE 표시·세이브 슬롯3·레벨업 타이니·치트(+10Lv)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>다음</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>귀여운 코스메틱 스킨(윤리적 수익화) / 포식(Devour)</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,19 @@
           <t>다음</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -17,9 +17,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DynamicDifficulty" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herald_충신" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -852,168 +855,248 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>상수</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>baseMaxHp</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>시작 최대 체력</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>달성 시 송곳니 보상 + 슬롯별 영구 기록. 사망 시 평가.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>baseSpeed</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>기본 이동속도(px/s)</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>보상(송곳니)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>pickupRange</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>58</v>
+          <t>kill10</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>구슬 수집 기본 범위</t>
-        </is>
+          <t>첫 사냥</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>적 10 처치</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>xpStart</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
+          <t>surv60</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>레벨1 요구 XP</t>
-        </is>
+          <t>한 숨 돌리다</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>1분 생존</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>xpGrowth</t>
+          <t>lv10</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>prev×1.26+2</t>
+          <t>⭐</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>다음 레벨 요구 XP</t>
-        </is>
+          <t>성장하는 맹수</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>레벨 10</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>enemyCap</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>120</v>
+          <t>stage5</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>🌊</t>
+        </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>동시 최대 적</t>
-        </is>
+          <t>거센 파도</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>스테이지 5</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>bossInterval</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>90</v>
+          <t>kill100</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>💀</t>
+        </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>보스 주기(초)</t>
-        </is>
+          <t>학살자</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>한 판 100킬</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>rageMax</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>75</v>
+          <t>boss1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>광기 게이지 최대</t>
-        </is>
+          <t>거수 사냥꾼</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>보스 처치</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>diffRange</t>
+          <t>dev200</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>0.6~2.2</t>
+          <t>🍖</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>동적 난이도 배수 범위</t>
-        </is>
+          <t>대식가</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>한 판 200 포식</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>surv180</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>살아있는 전설</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>3분 생존</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +1110,453 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>윤리적 수익화 — 색만 바꾸는 코스메틱(P2W 없음). 송곳니로 해금·착용. 슬롯별 저장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>색</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>비용(송곳니)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>🐯</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>기본(캐릭터색)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>캐릭터별</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>snow</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>❄</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>눈호랑이</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>0xFFBFE8F5</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>shadow</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>🌑</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>그림자 표범</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>0xFFB07CE0</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ember</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>잿불 맹수</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>0xFFE8702E</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>🍃</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>비취 야수</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>0xFF7FD08A</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>royal</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>👑</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>황금 폭군</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>0xFFFFD54F</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>요소</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>포식 회복</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>처치=삼킴 → 회복(잡몹0.6/쾌속0.4/탱크2.5/보스12, 풀피 시 미발동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>호랑이 성장</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>growScale 0.9→1.6(처치 누적, 시각만·히트박스 유지) = 양→호랑이</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>데일리 보너스</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>하루 첫 접속 송곳니 +30(비강제). lastDaily 슬롯별 저장</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>상수</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>baseMaxHp</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>시작 최대 체력</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>baseSpeed</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>기본 이동속도(px/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>pickupRange</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>구슬 수집 기본 범위</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>xpStart</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>레벨1 요구 XP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>xpGrowth</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>prev×1.26+2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>다음 레벨 요구 XP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>enemyCap</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>동시 최대 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>bossInterval</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>보스 주기(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>rageMax</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>광기 게이지 최대</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>diffRange</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>0.6~2.2</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>동적 난이도 배수 범위</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1181,34 +1710,58 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>귀여운 코스메틱 스킨(윤리적 수익화) / 포식(Devour)</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>펫 타이니(따라다니며 표정 반응)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>다음</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>포식(Devour)+호랑이 성장 / 업적 8종 / 코스메틱 스킨6 / 데일리 보너스</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>보스 패턴·서사 / 무기·캐릭터 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>다음</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>
@@ -1219,7 +1772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -1556,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1734,24 +1734,24 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>보스 패턴·서사 / 무기·캐릭터 해금</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>스테이지 선택(클리어한 곳까지) / 펫 360°추적·말풍선 / 스킬 데미지표시 / 메뉴 빌드상태·스테이지± / 치트=스킬선택</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>다음</t>
+          <t>다음★</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+          <t>보스 패턴·서사 / 무기·캐릭터 해금</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,19 @@
           <t>다음</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -8,21 +8,22 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolutions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passives" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultimate_광기" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DynamicDifficulty" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herald_충신" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specials_특별스킬" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolutions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passives" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemies" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultimate_광기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages_스테이지" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herald_충신" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,13 +51,13 @@
       <color rgb="00F3D89A"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="009C8C7E"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00F3D89A"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="009C8C7E"/>
     </font>
   </fonts>
   <fills count="3">
@@ -103,13 +104,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -623,6 +624,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>전부 텍스트(무음). 표시 3.2초·쿨 0.8초. 맥락 없는 잡담·랜덤 멘트 제거(상황 맞는 것만).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>트리거</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>발동 시점</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>강제표시</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>예시 대사</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>greet</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>런 시작</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>대장님, 곁을 지키겠습니다. 사냥의 시간입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>레벨업</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>또 강해지셨습니다, 대장님!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>tiger</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Lv5·Lv13 변신</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>대장님… 더는 양이 아니십니다. 호랑이의 눈빛입니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>보스 격파</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>보셨습니까! 거수가 대장님 발톱에 찢겼습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ult</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>어흥! 궁극</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>크하핫—! 대륙이 대장님 포효 앞에 무릎 꿇습니다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>HP&lt;25%(9초쿨)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>대장님, 위험합니다 — 잠시 물러서시죠!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>streak</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>30킬마다</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>대장님 지나간 자리엔 시체만 쌓입니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>1·2·3분 생존</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>3분 생존… 대장님은 이미 살아있는 전설이십니다!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -636,209 +862,209 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>화폐=송곳니. 사망 시 적립: (킬+생존초+레벨×8)×(1+0.12×gain Lv). 비용=기본가×1.55^Lv. localStorage 영구 저장.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>효과(레벨당)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>기본가</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>최대Lv</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>비용증가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>atk</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>💪</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>맹수의 발톱</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>시작 공격력 +5%</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>❤</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>두꺼운 가죽</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>시작 체력 +15</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>spd</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>🌬</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>바람의 다리</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>시작 이동속도 +4%</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>pick</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>🧲</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>굶주린 코</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>수집 범위 +8</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>×1.55</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>gain</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>🦷</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>전리품 사냥꾼</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>송곳니 획득 +12%</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>×1.55</t>
         </is>
@@ -849,7 +1075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -866,236 +1092,236 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>달성 시 송곳니 보상 + 슬롯별 영구 기록. 사망 시 평가.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>조건</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>보상(송곳니)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>kill10</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>🩸</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>첫 사냥</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>적 10 처치</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>surv60</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>한 숨 돌리다</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>1분 생존</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>lv10</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>성장하는 맹수</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>레벨 10</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>stage5</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>🌊</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>거센 파도</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>스테이지 5</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>kill100</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>💀</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>학살자</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>한 판 100킬</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>boss1</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>👹</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>거수 사냥꾼</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>보스 처치</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>dev200</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>🍖</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>대식가</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>한 판 200 포식</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>surv180</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>🏆</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>살아있는 전설</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>3분 생존</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1104,7 +1330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1121,186 +1347,186 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>윤리적 수익화 — 색만 바꾸는 코스메틱(P2W 없음). 송곳니로 해금·착용. 슬롯별 저장.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>색</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>비용(송곳니)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>🐯</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>기본(캐릭터색)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>캐릭터별</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>snow</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>❄</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>눈호랑이</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>0xFFBFE8F5</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>shadow</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>🌑</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>그림자 표범</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>0xFFB07CE0</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ember</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>잿불 맹수</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>0xFFE8702E</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>jade</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>🍃</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>비취 야수</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>0xFF7FD08A</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>royal</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>👑</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>황금 폭군</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>0xFFFFD54F</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1309,7 +1535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1323,19 +1549,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>요소</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>포식 회복</t>
         </is>
@@ -1347,7 +1573,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>호랑이 성장</t>
         </is>
@@ -1359,7 +1585,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>데일리 보너스</t>
         </is>
@@ -1367,181 +1593,6 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>하루 첫 접속 송곳니 +30(비강제). lastDaily 슬롯별 저장</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>상수</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>baseMaxHp</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>시작 최대 체력</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>baseSpeed</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>156</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>기본 이동속도(px/s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>pickupRange</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>구슬 수집 기본 범위</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>xpStart</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>레벨1 요구 XP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>xpGrowth</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>prev×1.26+2</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>다음 레벨 요구 XP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>enemyCap</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>동시 최대 적</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>bossInterval</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>보스 주기(초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>rageMax</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>광기 게이지 최대</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>diffRange</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>0.6~2.2</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>동적 난이도 배수 범위</t>
         </is>
       </c>
     </row>
@@ -1556,226 +1607,182 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>항목</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>상수</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>설명</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>네온 아트 + 손맛(데미지숫자·흔들림·파티클)</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>baseMaxHp</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>시작 최대 체력</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>코드 합성 사운드(효과음7 + 음소거)</t>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>baseSpeed</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>기본 이동속도(px/s)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>무기 진화 + 신무기(벼락·가시밭)</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>pickupRange</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>구슬 수집 기본 범위(+자성80)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>캐릭터 3종</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>xpStart</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>레벨1 요구 XP</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>초반 난이도 완화</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>xpGrowth</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>prev×1.22+2</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>다음 레벨 요구 XP(살짝 완화→더 잦은 강화)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>조작 개선 + 어흥! 궁극 + 스토리 도입</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>enemyCap</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>동시 최대 적</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>충신 herald 시스템(무음 텍스트)</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>bossInterval</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>보스 주기(초)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>타이니 동적 난이도 선택 대화</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>rageMax</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>광기 게이지 최대</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>메타 영구강화(송곳니 화폐 → 전리품 상점) + 위협도 표시</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>0.78+(stage-1)×0.07</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>스테이지 난이도(clamp 0.6~3.0)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>무해·귀여움 컨셉: 캐릭터 절차 애니메이션(숨쉬기·통통·눈깜빡·꼬리)+캐릭터별 외형, 타이니 등장연출</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>타이니 호출 메뉴·고정 반투명 조이스틱·STAGE 표시·세이브 슬롯3·레벨업 타이니·치트(+10Lv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>펫 타이니(따라다니며 표정 반응)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>포식(Devour)+호랑이 성장 / 업적 8종 / 코스메틱 스킨6 / 데일리 보너스</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>스테이지 선택(클리어한 곳까지) / 펫 360°추적·말풍선 / 스킬 데미지표시 / 메뉴 빌드상태·스테이지± / 치트=스킬선택</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>보스 패턴·서사 / 무기·캐릭터 해금</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>다음</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>무기/캐릭터 해금(송곳니) / 보스 패턴·서사</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>다음</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>specialEvery</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>특별스킬 선택 주기(레벨)</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1797,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>네온 아트 + 손맛(데미지숫자·흔들림·파티클)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>코드 합성 사운드(효과음7 + 음소거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>무기 진화 + 신무기(벼락·가시밭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 3종</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>초반 난이도 완화</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>조작 개선 + 어흥! 궁극 + 스토리 도입</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>충신 herald 시스템(무음 텍스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>타이니 동적 난이도 선택 대화</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>메타 영구강화(송곳니 화폐 → 전리품 상점) + 위협도 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>무해·귀여움 컨셉: 캐릭터 절차 애니메이션(숨쉬기·통통·눈깜빡·꼬리)+캐릭터별 외형, 타이니 등장연출</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>타이니 호출 메뉴·고정 반투명 조이스틱·STAGE 표시·세이브 슬롯3·레벨업 타이니·치트(+10Lv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>펫 타이니(따라다니며 표정 반응)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>포식(Devour)+호랑이 성장 / 업적 8종 / 코스메틱 스킨6 / 데일리 보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>스테이지 선택(클리어한 곳까지) / 펫 360°추적·말풍선 / 스킬 데미지표시 / 메뉴 빌드상태·스테이지± / 치트=스킬선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>단일 주인공 '호랑이가 되고 싶은 양'(양→호랑이 모핑) / 특별스킬 10종(10레벨마다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>적 8종 확장(swarm·splitter·bomber·shooter+투사체) / 스테이지 페이싱 완화 / 스킬 밸런스 재검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>세이브 삭제 / 타이니 버튼 불투명 / 포기→사냥터 이동 버튼 / 대사 정리(맥락 없는 멘트 제거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1798,60 +2063,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>legacy</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>투자 은유 카드게임(폐기, 로컬 v28.0 아카이브)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>피벗1</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>텍스트 선택지 → Reigns식 스와이프 카드</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>피벗2</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>뱀파이어 서바이버즈류(현재)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>개편</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>단일 주인공(양→호랑이 모핑)·특별스킬10·적8종·페이싱 완화·세이브삭제·사냥터이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>이후</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>git 커밋 로그로 추적</t>
         </is>
@@ -1872,162 +2149,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>아이콘</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>시작무기</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>공격</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>체력</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>이동</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>콘셉트</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>white</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>백호 부족장</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>🐯</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>발톱</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>균형</t>
+          <t>tigerProg=((level-1)/13 + devour/700) clamp 0~1. 0=양(양털·둥근귀·순한눈), 1=호랑이(줄무늬 마스크·뾰족귀·송곳니·사나운 눈매). 양→호랑이 USP를 외형으로 직접 구현.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>그림자 흑표</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>🐆</t>
+          <t>아이콘</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>송곳니</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>1.12</v>
+          <t>시작무기</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>체력</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>이동</t>
+        </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>유리대포(고위험)</t>
+          <t>콘셉트</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>iron</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>무쇠뿔 들소</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>🐃</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>포효</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>탱크(저속·고체력)</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>lamb</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>호랑이가 되고 싶은 양</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>🐑→🐯</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>발톱</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>단일 주인공. 양으로 시작→레벨/포식으로 외형이 호랑이로 모핑(tigerProg)</t>
         </is>
       </c>
     </row>
@@ -2055,221 +2267,221 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>데미지엔 dmgMult(야성·캐릭터·광폭화), 쿨다운엔 fireMult(분노·광폭화) 적용</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>데미지엔 dmgMult(야성·캐릭터·광폭화·맹수의격), 쿨다운엔 fireMult(분노·광폭화·과부하) 적용</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>쿨다운</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>데미지</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>핵심 스케일</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>최대Lv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>claw</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>발톱 폭풍</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>투사체</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>0.8×0.9^(Lv-1)/fireMult</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>9+Lv×4</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>투사체 1(+@2,4,6)·관통@5</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>투사체 1(+@2,4,6·분신+1)·관통@5</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>fang</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>회전 송곳니</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>궤도 DPS</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>상시</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>DPS 22+Lv×14</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>DPS 20+Lv×12</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>개수=Lv·반경60+Lv×4·접촉13</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>roar</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>포효</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>즉발 광역</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>2.6×0.93^(Lv-1)/fireMult</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>8+Lv×7</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>반경70+Lv×16·넉백14</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>bolt</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>벼락</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>연쇄 번개</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1.5×0.9^(Lv-1)/fireMult</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>10+Lv×6</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>연쇄1+Lv·사정210·×0.82</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>spike</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>가시밭</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>광역 지대</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>1.8×0.92^(Lv-1)/fireMult</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>8+Lv×6</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>반경70+Lv×16·넉백14</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>bolt</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>벼락</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>연쇄 번개</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1.5×0.9^(Lv-1)/fireMult</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>10+Lv×6</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>연쇄1+Lv·사정210·×0.82</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>spike</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>가시밭</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>광역 지대</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>1.8×0.92^(Lv-1)/fireMult</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>8+Lv×5</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>반경42+Lv×7·오프셋±160</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2279,6 +2491,331 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>10레벨마다 1개 선택(중복 불가). 보유하지 않은 것 중 3택. regen/lifesteal 선택 시 즉시 체력 15% 회복.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>구현</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>fury</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>🐯</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>맹수의 격</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>모든 공격력 +25%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>dmgMult ×1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>haste</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>과부하</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>공격 속도 +30%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>fireMult ×1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>🛡</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>강철 가죽</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>받는 피해 −22%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>접촉/투사체 피해 ×0.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>slow</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>🕸</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>거미줄 본능</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>모든 적 이동속도 −18%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>enemy speed ×0.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>magnet</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>🧲</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>굶주린 포식</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>수집 범위 대폭↑ · 경험치 +30%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>pickupRange +80, XP ×1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>regen</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>💗</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>재생</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>매초 체력 서서히 회복</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>+maxHp×1.2%/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>lifesteal</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>흡혈</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>처치 시 회복량 3배</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>heal ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>explode</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>연쇄 폭발</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>적 처치 시 주변 폭발</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>반경58, (12+Lv×2)×dmgMult</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>🌪</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>분신 발톱</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>발톱 투사체 +1줄기</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>claw n +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>❄</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>서리 손길</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>맞은 적 1.2초 둔화</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>chill → speed ×0.4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2294,95 +2831,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>레벨업 시 조건 충족하면 진화 선택지 우선 노출 (뱀서의 핵심 훅)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>진화무기</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>원본</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>조건</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>효과</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>천 개의 발톱</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>claw</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>발톱 Lv8 + 분노 Lv3</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>16발 전방위·데미지×1.7·관통3·쿨0.5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>죽음의 고리</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>fang</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>송곳니 Lv6 + 야성 Lv3</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>개수+3·반경×1.4·DPS×1.9·접촉17</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>대지진</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>roar</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>포효 Lv7 + 가죽 Lv3</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>반경×1.8·데미지×2.2·넉백30</t>
         </is>
@@ -2393,7 +2930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2408,311 +2945,104 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>레벨당 효과</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>wild</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>야성</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>공격력 +12%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>hide</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>가죽</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>최대체력 +25, 즉시 25 회복</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>wind</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>바람</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>이동속도 +10%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>hunger</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>굶주림</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>수집범위 +16</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>rage</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>분노</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>공속 +10%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>t=생존 경과 초, diff=동적 난이도 배수. 스폰: 시작1.4s·간격 max(0.5,2.0-0.011t)·1회 1+(t÷48)·최대120체</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>타입</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>이동속도</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>접촉피해</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>반경</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>등장</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>드랍</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>grunt 잡몹</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>(9+0.5t)×diff</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>44+0.12t</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>(4.5+0.03t)×diff</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>항상</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>구슬1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>fast 쾌속</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>(9+0.5t)×0.65×diff</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>72+0.17t</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>(4+0.03t)×diff</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>t&gt;42, 32%</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>구슬1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>tank 탱크</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>(9+0.5t)×3.0×diff</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>30+0.05t</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>(8.5+0.05t)×diff</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>t&gt;78, 13%</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>구슬3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>boss 보스</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>(240+6t)×diff</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>(22+0.08t)×diff</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>90초마다</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>구슬14</t>
         </is>
       </c>
     </row>
@@ -2722,6 +3052,353 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>base=(9+0.5t)×diff. t=생존초, diff=스테이지 난이도. 스폰: 시작1.4s·간격 max(0.5,2.0-0.011t)·1회 1+(t÷48)·최대120체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>HP(×base)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>이동속도</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>접촉피해</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>해금</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>grunt 잡몹</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>base ×1</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>44+0.12t</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>(4.5+0.03t)×diff</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>항상</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>구슬1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>fast 쾌속</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>base ×0.65</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>72+0.17t</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>(4+0.03t)×diff</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>t&gt;26</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>구슬1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>swarm 떼거리</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>base ×0.4</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>90+0.2t</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>(3+0.02t)×diff</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>STAGE≥2</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>약하고 빠름·다수</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>tank 탱크</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>base ×3.0</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>30+0.05t</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>(8.5+0.05t)×diff</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>t&gt;70</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>구슬3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>splitter 분열</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>base ×1.3</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>40+0.08t</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>(5+0.03t)×diff</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>STAGE≥3</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>죽으면 swarm 2마리로 분열</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>shooter 원거리</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>base ×0.8</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>26+0.05t</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>(4+0.02t)×diff</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>STAGE≥4</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2.2초마다 투사체(피해 e.dmg×1.4+3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>bomber 자폭</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>base ×0.9</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>54+0.12t</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>(4+0.02t)×diff</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>STAGE≥5</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>죽을 때 반경72 폭발(16+0.1t)×diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>boss 거수</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>(240+6t)×diff</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>(22+0.08t)×diff</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>90초마다</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>구슬14·체력링</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2735,63 +3412,63 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>게이지 최대</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>충전</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>잡몹+1 / 탱크+3 / 보스+14 (×diff)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>해방 피해</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>60+레벨×12 (전 적)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>넉백</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>광폭화</t>
         </is>
@@ -2799,143 +3476,6 @@
       <c r="B6" s="7" t="inlineStr">
         <is>
           <t>5초 · 공속×1.6 · 공격×1.35 · 이동×1.18</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>diff 0.6~2.2(시작 1.0). 높을수록 적 강함 + XP·광기 획득 ×diff(빠른 성장). 선택 후 32초 쿨다운.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>상황</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>발동 조건</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>선택 → 효과</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>타이니 반응</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>후퇴 제안</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>HP&lt;32% &amp; diff&gt;0.65</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>물러난다 → diff−0.4·체력35%회복·적정리</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>호랑이는 물러설 때를 아는 법이죠</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>(후퇴 거절)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>계속 사냥 → 광기 +30%</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>역시 호랑이답습니다! 물러섬을 모르는 분!</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>진격 제안</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>HP&gt;60% &amp; ~55초마다 &amp; diff&lt;2.0</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>쳐들어간다 → diff+0.45</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>이래야 맛이 나죠! 방심하면 한 입에 끝</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>(진격 거절)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>천천히 간다 → 변동 없음</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>신중함도 맹수의 덕목이죠</t>
         </is>
       </c>
     </row>
@@ -2950,195 +3490,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>전부 텍스트(무음) → 회사에서 몰래 해도 소리 없이 뽕. 표시 2.8초·쿨 0.8초.</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>구 '동적 난이도 대화(후퇴/진격)'는 제거 — 포기 대신 STAGE 이동으로 대체(로그라이트 즉시-재시작).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>트리거</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>발동 시점</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>강제표시</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>예시 대사</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>설명</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>greet</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>런 시작</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>대장님, 오늘도 의회 놈들의 간담을 서늘하게 해주시죠.</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>난이도 공식</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>diff = 0.78+(stage-1)×0.07</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>한 칸 간극 완만(급상승 방지). clamp 0.6~3.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>레벨업</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>또 강해지셨습니까?! 누가 감히 대장님을 양이라 했습니까!</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>자동 상승 간격</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>13+stage×2.2 (cap 38s)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>초반 빠름(약15s)→갈수록 김 = 빠른 진행감</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>boss</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>보스 격파</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>보셨습니까! 의회의 거수가 대장님 발톱에 찢겼습니다!</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>XP·광기 획득</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>×diff (자성 시 XP ×1.3 추가)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>stage 높을수록 빠른 성장</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ult</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>어흥! 궁극</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>크하핫—! 대륙이 대장님 포효 앞에 무릎 꿇습니다!!</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>사냥터 이동</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 ±선택 → [이동] 확정</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>HP&lt;25%(9초쿨)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>이건 일부러 봐주시는 거죠…? 그렇죠?!</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>streak</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>30킬마다</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>대장님 지나간 자리엔 시체만 쌓입니다!</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1·2·3분 생존</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>3분 생존… 대장님은 이미 살아있는 전설이십니다!</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>maxStage 저장</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>슬롯별 영구(localStorage)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>도달한 최고 스테이지까지만 이동 가능</t>
         </is>
       </c>
     </row>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -20,10 +20,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickups_파워업" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1541,6 +1544,355 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>근거: VS류 바닥 아이템 = 순간 변수·전술·도파민. 보스는 픽업 대신 전리품 상자.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>드랍/발동</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>magnet 자석</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>🧲</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>화면의 마나구슬 전부 즉시 흡수(+XP)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>탱크16%·분열6%·일반2.2%·보스X</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>bomb 폭탄</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>💣</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>화면 전체 광역 피해 (50+Lv×9)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>가까우면 끌려옴·닿으면 발동</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>heal 회복</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>❤</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>최대체력 32% 회복</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>수명 13초·최대 6개·사라지기 전 깜빡임</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>근거: VS 보물상자 = 강력한 보상 스파이크 + 빌드 가속 도파민.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>획득</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>보스 처치 시 freePicks +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>무료 강화 선택 1회(레벨업 화면 재사용·진화도 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>첫 보스</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>60초(초반 보상 스파이크) · 이후 90초 주기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>연출</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>🎁 펄스+흔들림+사운드, 타이니 '전리품 상자!'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>((stage-1)//3)%5로 순환. 부유 모트(18개, time기반 무상태)로 살아있는 배경. 근거: 반복 맵=지루함 1순위.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>티어</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>스테이지</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>분위기</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>색감</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>둥지(황혼 황금)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>0xFF15110C→070605 / 그리드·모트 골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>4–6</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>핏빛 전장</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>0xFF1A0D0B→0A0504 / 붉은톤</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>7–9</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>시린 한밤</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0xFF0D1018→05070A / 청록톤</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>10–12</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>보라 의회</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0xFF120A1A→070409 / 보라톤</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>13–15</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>비취 심림</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>0xFF0A1410→050806 / 초록톤</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1601,7 +1953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1791,13 +2143,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2023,114 +2375,36 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>재미강화(리서치): 바닥 파워업 픽업 / 보스 전리품 상자(무료강화) / 스테이지 테마 배경+모트 / 빈슬롯 데일리버그 수정 / 사장코드 제거</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>다음</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>legacy</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>투자 은유 카드게임(폐기, 로컬 v28.0 아카이브)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>피벗1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>텍스트 선택지 → Reigns식 스와이프 카드</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>피벗2</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>뱀파이어 서바이버즈류(현재)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>개편</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>단일 주인공(양→호랑이 모핑)·특별스킬10·적8종·페이싱 완화·세이브삭제·사냥터이동</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>이후</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>git 커밋 로그로 추적</t>
         </is>
       </c>
     </row>
@@ -2248,6 +2522,96 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>투자 은유 카드게임(폐기, 로컬 v28.0 아카이브)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>피벗1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>텍스트 선택지 → Reigns식 스와이프 카드</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>피벗2</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>뱀파이어 서바이버즈류(현재)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>개편</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>단일 주인공(양→호랑이 모핑)·특별스킬10·적8종·페이싱 완화·세이브삭제·사냥터이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>이후</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>git 커밋 로그로 추적</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -21,12 +21,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickups_파워업" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear_장비" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1659,6 +1660,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>RPG식 3슬롯 장비. 영구 보유·장착(슬롯별). 획득=보스 전리품 루트(60%, 낮은 레어도 가중)+대장간 구매. 가챠·다크패턴 없음. 상태·장비 화면에서 장착/구매. 근거: Death Must Die/Halls of Torment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>슬롯</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>레어도</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>구매가(송곳니)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>w0</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>무기</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>무쇠 발톱</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>공격력 +8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>w1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>무기</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>예리한 발톱</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>공격력 +14% · 공속 +8%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>w2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>무기</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>폭풍의 발톱</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>공격력 +22% · 공속 +14%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>w3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>무기</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>백호의 발톱</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>공격력 +34% · 공속 +18%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>a0</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>방어구</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>두꺼운 가죽</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>최대체력 +35</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>방어구</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>상흔의 가죽</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>체력 +60 · 재생 0.5/s</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>방어구</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>강철 비늘</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>체력 +95 · 재생 1.0/s</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>a3</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>방어구</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>불멸의 가죽</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>체력 +150 · 재생 1.6/s</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>t0</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>장신구</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>바람 부적</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>이동 +6% · 수집 +12</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>장신구</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>탐욕의 부적</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>이동 +8% · 수집 +26</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>장신구</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>사냥꾼의 부적</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>이동 +12% · 수집 +30 · 공속 +8%</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>장신구</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>폭군의 인장</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>이동 +14% · 공격 +12% · 수집 +30</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1738,7 +2160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1887,7 +2309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1932,7 +2354,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>growScale 0.9→1.6(처치 누적, 시각만·히트박스 유지) = 양→호랑이</t>
+          <t>크기 거의 고정(1.0→1.08·tigerProg) — 무한정 X. 성장은 양→호랑이 모핑이 전담</t>
         </is>
       </c>
     </row>
@@ -1953,7 +2375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2135,276 +2557,6 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>특별스킬 선택 주기(레벨)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>네온 아트 + 손맛(데미지숫자·흔들림·파티클)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>코드 합성 사운드(효과음7 + 음소거)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>무기 진화 + 신무기(벼락·가시밭)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>캐릭터 3종</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>초반 난이도 완화</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>조작 개선 + 어흥! 궁극 + 스토리 도입</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>충신 herald 시스템(무음 텍스트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>타이니 동적 난이도 선택 대화</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>메타 영구강화(송곳니 화폐 → 전리품 상점) + 위협도 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>무해·귀여움 컨셉: 캐릭터 절차 애니메이션(숨쉬기·통통·눈깜빡·꼬리)+캐릭터별 외형, 타이니 등장연출</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>타이니 호출 메뉴·고정 반투명 조이스틱·STAGE 표시·세이브 슬롯3·레벨업 타이니·치트(+10Lv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>펫 타이니(따라다니며 표정 반응)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>포식(Devour)+호랑이 성장 / 업적 8종 / 코스메틱 스킨6 / 데일리 보너스</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>스테이지 선택(클리어한 곳까지) / 펫 360°추적·말풍선 / 스킬 데미지표시 / 메뉴 빌드상태·스테이지± / 치트=스킬선택</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>단일 주인공 '호랑이가 되고 싶은 양'(양→호랑이 모핑) / 특별스킬 10종(10레벨마다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>적 8종 확장(swarm·splitter·bomber·shooter+투사체) / 스테이지 페이싱 완화 / 스킬 밸런스 재검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>세이브 삭제 / 타이니 버튼 불투명 / 포기→사냥터 이동 버튼 / 대사 정리(맥락 없는 멘트 제거)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>재미강화(리서치): 바닥 파워업 픽업 / 보스 전리품 상자(무료강화) / 스테이지 테마 배경+모트 / 빈슬롯 데일리버그 수정 / 사장코드 제거</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>다음</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>
       </c>
     </row>
@@ -2528,6 +2680,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>네온 아트 + 손맛(데미지숫자·흔들림·파티클)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>코드 합성 사운드(효과음7 + 음소거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>무기 진화 + 신무기(벼락·가시밭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>캐릭터 3종</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>초반 난이도 완화</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>조작 개선 + 어흥! 궁극 + 스토리 도입</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>충신 herald 시스템(무음 텍스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>타이니 동적 난이도 선택 대화</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>메타 영구강화(송곳니 화폐 → 전리품 상점) + 위협도 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>무해·귀여움 컨셉: 캐릭터 절차 애니메이션(숨쉬기·통통·눈깜빡·꼬리)+캐릭터별 외형, 타이니 등장연출</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>타이니 호출 메뉴·고정 반투명 조이스틱·STAGE 표시·세이브 슬롯3·레벨업 타이니·치트(+10Lv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>펫 타이니(따라다니며 표정 반응)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>포식(Devour)+호랑이 성장 / 업적 8종 / 코스메틱 스킨6 / 데일리 보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>스테이지 선택(클리어한 곳까지) / 펫 360°추적·말풍선 / 스킬 데미지표시 / 메뉴 빌드상태·스테이지± / 치트=스킬선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>단일 주인공 '호랑이가 되고 싶은 양'(양→호랑이 모핑) / 특별스킬 10종(10레벨마다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>적 8종 확장(swarm·splitter·bomber·shooter+투사체) / 스테이지 페이싱 완화 / 스킬 밸런스 재검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>세이브 삭제 / 타이니 버튼 불투명 / 포기→사냥터 이동 버튼 / 대사 정리(맥락 없는 멘트 제거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>재미강화(리서치): 바닥 파워업 픽업 / 보스 전리품 상자(무료강화) / 스테이지 테마 배경+모트 / 빈슬롯 데일리버그 수정 / 사장코드 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>RPG화(리서치): 장비 시스템(3슬롯·레어도·스탯·보스루트·대장간) / 상태·장비 화면 / 시작스테이지 선택 / 고스테이지 XP·전리품↑ / 난이도 하향 / 크기 고정 / 메뉴 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3854,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3894,12 +4328,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>diff = 0.78+(stage-1)×0.07</t>
+          <t>diff = 0.62+(stage-1)×0.055</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>한 칸 간극 완만(급상승 방지). clamp 0.6~3.0</t>
+          <t>하향 조정(너무 높다는 피드백). clamp 0.5~2.4</t>
         </is>
       </c>
     </row>
@@ -3923,49 +4357,66 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>XP·광기 획득</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>×diff (자성 시 XP ×1.3 추가)</t>
+          <t>XP 획득</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>구슬 × xpMult(=1+(stage-1)×0.2) · 자성 ×1.3</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>stage 높을수록 빠른 성장</t>
+          <t>고스테이지일수록 XP↑(빠른 성장 보상)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>사냥터 이동</t>
+          <t>시작 스테이지</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>메뉴 ±선택 → [이동] 확정</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
+          <t>타이틀·사망 화면 버튼 선택(~maxStage)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>고스테이지 시작=적 강함+XP·전리품↑</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>사냥터 이동</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 ±선택 → [이동] 확정</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>maxStage 저장</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>슬롯별 영구(localStorage)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>도달한 최고 스테이지까지만 이동 가능</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -4288,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4391,32 +4391,49 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>사냥터 이동</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>메뉴 ±선택 → [이동] 확정</t>
+          <t>적 스케일 시간</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>scaleT = 생존시간 + headStart(시작스테이지 누적시간)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
+          <t>고스테이지 시작=그 스테이지까지 플레이한 강함과 동일(생존시간은 0부터)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>사냥터 이동</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 ±선택 → [이동] 확정</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>maxStage 저장</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>슬롯별 영구(localStorage)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>도달한 최고 스테이지까지만 이동 가능</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -4288,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4408,32 +4408,49 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>사냥터 이동</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>메뉴 ±선택 → [이동] 확정</t>
+          <t>시작 빌드 자동</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>picks≈(stage-1)×1.7 · level=1+picks · 특별스킬 floor(lv/10)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
+          <t>레벨1 맨몸 문제 해결 — 시작스테이지만큼 무기/패시브/체력/레벨 자동 지급(편의)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>사냥터 이동</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>메뉴 ±선택 → [이동] 확정</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>maxStage까지. 낮추면 수월·올리면 보상↑. 이동 시 체력 15% 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>maxStage 저장</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>슬롯별 영구(localStorage)</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>도달한 최고 스테이지까지만 이동 가능</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -2315,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2337,34 +2337,46 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>포식 회복</t>
+          <t>포식 누적 성장</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>처치=삼킴 → 회복(잡몹0.6/쾌속0.4/탱크2.5/보스12, 풀피 시 미발동)</t>
+          <t>처치당 공격력 +0.35% · 공속 +0.18%(연속·상한없음). 레벨=빌드방향/포식=누적파워 역할분리</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>호랑이 성장</t>
+          <t>포식 회복</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>크기 거의 고정(1.0→1.08·tigerProg) — 무한정 X. 성장은 양→호랑이 모핑이 전담</t>
+          <t>처치=삼킴 → 회복(잡몹0.6/쾌속0.4/탱크2.5/보스12, 풀피 시 미발동)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>호랑이 성장</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>크기 거의 고정(1.0→1.08·tigerProg) — 무한정 X. 성장은 양→호랑이 모핑이 전담</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
           <t>데일리 보너스</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>하루 첫 접속 송곳니 +30(비강제). lastDaily 슬롯별 저장</t>
         </is>
@@ -4362,12 +4374,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>구슬 × xpMult(=1+(stage-1)×0.2) · 자성 ×1.3</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>고스테이지일수록 XP↑(빠른 성장 보상)</t>
+          <t>구슬 × xpMult(=1+(stage-1)×0.1) · 자성 ×1.3</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>스테이지 보너스 완화(누적 성장이 고스테이지 파워 담당)</t>
         </is>
       </c>
     </row>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -20,14 +20,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickups_파워업" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear_장비" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameFeel_게임필" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickups_파워업" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear_장비" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1545,6 +1546,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>검증된 게임필(juice) 기법. 과용은 역효과라 세기·빈도 절제(히트스톱 쿨다운·낮은 플래시).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>기법</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>수치</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>트리거</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>크리티컬</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>확률 12% · 데미지 ×2 · 금색 큰 숫자</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>발톱·포효·벼락·가시밭 단발 타격</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>타격 변별·쾌감</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>히트스톱</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>dt ×0.12, 0.045~0.09s · 쿨다운 0.22s</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>크리/보스/엘리트/어흥</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>타격감(연구: 3~5프레임 정지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>콤보</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>연속처치 누적 → 공격 +최대24%(0.4%/콤보,cap60) · 유지 2.4s</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>처치마다 +1, 10콤보마다 연출</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>도파민·고조</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>스크린 플래시</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>전체 발광 opacity ≤0.32, 빠른 감쇠</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>레벨업0.35·어흥0.7·보스0.6·엘리트0.5</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>임팩트(절제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>엘리트 적</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>확률 4.5%(scaleT&gt;35) · HP×3.2·반경×1.35·피해×1.25</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>처치 시 픽업+송곳니8+포식6 확정</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>우선타겟·긴장·보상</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1654,7 +1814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2075,7 +2235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2160,7 +2320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2309,7 +2469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2379,196 +2539,6 @@
       <c r="B5" s="7" t="inlineStr">
         <is>
           <t>하루 첫 접속 송곳니 +30(비강제). lastDaily 슬롯별 저장</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>상수</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>값</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>baseMaxHp</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>시작 최대 체력</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>baseSpeed</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>156</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>기본 이동속도(px/s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>pickupRange</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>구슬 수집 기본 범위(+자성80)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>xpStart</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>레벨1 요구 XP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>xpGrowth</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>prev×1.22+2</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>다음 레벨 요구 XP(살짝 완화→더 잦은 강화)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>enemyCap</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>동시 최대 적</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>bossInterval</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>보스 주기(초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>rageMax</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>광기 게이지 최대</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>diff</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>0.78+(stage-1)×0.07</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>스테이지 난이도(clamp 0.6~3.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>specialEvery</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>특별스킬 선택 주기(레벨)</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2662,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>상수</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>baseMaxHp</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>시작 최대 체력</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>baseSpeed</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>기본 이동속도(px/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>pickupRange</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>구슬 수집 기본 범위(+자성80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>xpStart</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>레벨1 요구 XP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>xpGrowth</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>prev×1.22+2</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>다음 레벨 요구 XP(살짝 완화→더 잦은 강화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>enemyCap</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>동시 최대 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>bossInterval</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>보스 주기(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>rageMax</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>광기 게이지 최대</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>0.78+(stage-1)×0.07</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>스테이지 난이도(clamp 0.6~3.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>specialEvery</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>특별스킬 선택 주기(레벨)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2942,22 +3102,46 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>다음★</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>포식 누적 성장(처치할수록 연속 강화) — 레벨=빌드방향/포식=누적파워 역할분리 · 레벨폭주 완화</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>게임필 총동원(검증): 크리티컬·히트스톱·콤보미터·스크린플래시·엘리트 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>다음★</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>보스 패턴·서사 / 무기 해금(송곳니)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>다음</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>CanvasKit(스웜300+) / 엔드리스·데일리·리더보드</t>
         </is>
@@ -2968,7 +3152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -2662,7 +2662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2709,133 +2709,201 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>기본 이동속도(px/s)</t>
+          <t>기본 이동속도↑(속도감)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>pickupRange</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>58</v>
+          <t>fireMult 기본</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>×1.25</t>
+        </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>구슬 수집 기본 범위(+자성80)</t>
+          <t>기본 공속 상향(정신없는 탄막)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>xpStart</t>
+          <t>pickupRange</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>레벨1 요구 XP</t>
+          <t>구슬 수집 기본 범위↑(+자성80)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>xpGrowth</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>prev×1.22+2</t>
-        </is>
+          <t>xpStart</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>다음 레벨 요구 XP(살짝 완화→더 잦은 강화)</t>
+          <t>레벨1 요구 XP↓</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>enemyCap</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>120</v>
+          <t>xpGrowth</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>prev×1.18+2</t>
+        </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>동시 최대 적</t>
+          <t>더 잦은 레벨업(속도감·도파민)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>bossInterval</t>
+          <t>enemyCap</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>보스 주기(초)</t>
+          <t>동시 최대 적↑(화면 가득)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>rageMax</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>75</v>
+          <t>spawn</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>간격 max(0.32,1.7-0.012·scaleT) · 1회 1+(scaleT÷38)</t>
+        </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>광기 게이지 최대</t>
+          <t>더 자주·더 많이</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>enemyBase</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>0.78+(stage-1)×0.07</t>
+          <t>(6.5+0.34·scaleT)×diff</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>스테이지 난이도(clamp 0.6~3.0)</t>
+          <t>적 체력↓ → 즉사하듯 빠르게(쉬움 유지)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>접촉피해</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>×0.82 추가 완화</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>적이 많아져도 쉽게</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>bossInterval</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>보스 주기(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>rageMax</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>광기 최대↓(어흥 더 자주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>0.78+(stage-1)×0.07</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>스테이지 난이도(clamp 0.6~3.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t>specialEvery</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>특별스킬 선택 주기(레벨)</t>
         </is>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -20,15 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta_영구강화" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievements" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins_코스메틱" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameFeel_게임필" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickups_파워업" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear_장비" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options_옵션" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameFeel_게임필" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickups_파워업" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear_장비" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Treasure_전리품상자" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageThemes_배경" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Devour_Daily" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceConstants" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChangeLog" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1546,6 +1547,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>전역 저장(surv_opts, 슬롯 무관). 타이니 메뉴·타이틀 [⚙ 옵션]. 근거: 모바일/접근성 표준 옵션.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>옵션</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>소리</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>효과음 음소거 토글</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>진동(햅틱)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>기기 진동 on/off</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>화면 흔들림</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>스크린 셰이크 on/off</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>화면 번쩍임</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>스크린 플래시 on/off(광과민 접근성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>데미지 숫자</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>플로팅 데미지 숫자 on/off</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>조이스틱 위치</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>가운데</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>좌/중/우 선택</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1699,7 +1845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1814,7 +1960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2235,7 +2381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2320,7 +2466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2461,84 +2607,6 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>0xFF0A1410→050806 / 초록톤</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>요소</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>포식 누적 성장</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>처치당 공격력 +0.35% · 공속 +0.18%(연속·상한없음). 레벨=빌드방향/포식=누적파워 역할분리</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>포식 회복</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>처치=삼킴 → 회복(잡몹0.6/쾌속0.4/탱크2.5/보스12, 풀피 시 미발동)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>호랑이 성장</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>크기 거의 고정(1.0→1.08·tigerProg) — 무한정 X. 성장은 양→호랑이 모핑이 전담</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>데일리 보너스</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>하루 첫 접속 송곳니 +30(비강제). lastDaily 슬롯별 저장</t>
         </is>
       </c>
     </row>
@@ -2662,6 +2730,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>요소</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>포식 누적 성장</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>처치당 공격력 +0.35% · 공속 +0.18%(연속·상한없음). 레벨=빌드방향/포식=누적파워 역할분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>포식 회복</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>처치=삼킴 → 회복(잡몹0.6/쾌속0.4/탱크2.5/보스12, 풀피 시 미발동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>호랑이 성장</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>크기 거의 고정(1.0→1.08·tigerProg) — 무한정 X. 성장은 양→호랑이 모핑이 전담</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>데일리 보너스</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>하루 첫 접속 송곳니 +30(비강제). lastDaily 슬롯별 저장</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2914,7 +3060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3220,7 +3366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/AuhHeung_DB.xlsx
+++ b/docs/AuhHeung_DB.xlsx
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>가운데</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>좌/중/우 선택</t>
+          <t>엄지존(권장)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>왼쪽/엄지존(가운데-오른쪽,×0.66)/오른쪽 — 검증된 thumb-zone</t>
         </is>
       </c>
     </row>
